--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33251-2026 artfynd.xlsx
+++ b/artfynd/A 33251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137359312</v>
       </c>
       <c r="B2" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
